--- a/Documentacion Sprint (01 - 11)/Sprint 10 documentacion/Sprint_10_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 10 documentacion/Sprint_10_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 10 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 10 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19508A2A-826A-4EA4-AD41-1F3E9C8AAA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82B2E72-EC6D-49A3-A861-B5BB035289F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="248">
   <si>
     <t>ID</t>
   </si>
@@ -1050,9 +1050,6 @@
     <t>backend/src/services/cierre.service.js, backend/src/services/audit.service.js, matriz Sprint 10 – Grupo 5 CP-251 a CP-254</t>
   </si>
   <si>
-    <t>RESUMEN DE VELOCIDAD — Sprint 06</t>
-  </si>
-  <si>
     <t>Métrica</t>
   </si>
   <si>
@@ -1129,13 +1126,19 @@
   </si>
   <si>
     <t>100% PASS – CP-001 a CP-254</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
+  </si>
+  <si>
+    <t>RESUMEN DE VELOCIDAD — Sprint 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1245,8 +1248,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1301,8 +1311,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1369,11 +1384,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1393,6 +1424,63 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1402,9 +1490,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1423,23 +1508,17 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1447,91 +1526,12 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1623,6 +1623,41 @@
     <dxf>
       <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1637,13 +1672,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E1812F2-D3FD-4ED5-93FC-180E80B92822}" name="Tabla3" displayName="Tabla3" ref="A2:D14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E1812F2-D3FD-4ED5-93FC-180E80B92822}" name="Tabla3" displayName="Tabla3" ref="A2:D14" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D14" xr:uid="{7E1812F2-D3FD-4ED5-93FC-180E80B92822}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3412212-CB73-4BEF-9C74-DE98D9C34F49}" name="Métrica" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{6736C23A-399F-4B71-8121-B169B0B046DD}" name="Planificado" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{88B18FCC-CEC8-4ECF-86ED-803BCEFF1F31}" name="Realizado" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{97549F2B-1E48-41EE-A8AF-0E6C4A47B1DB}" name="Observación" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F3412212-CB73-4BEF-9C74-DE98D9C34F49}" name="Métrica" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{6736C23A-399F-4B71-8121-B169B0B046DD}" name="Planificado" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{88B18FCC-CEC8-4ECF-86ED-803BCEFF1F31}" name="Realizado" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{97549F2B-1E48-41EE-A8AF-0E6C4A47B1DB}" name="Observación" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1947,396 +1982,463 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="10" t="s">
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
     </row>
     <row r="4" spans="1:13" ht="24">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="33">
         <v>46188</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="10" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="33">
         <v>46192</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
     </row>
     <row r="5" spans="1:13" ht="122.25" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="10" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" spans="1:13" ht="24">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="10" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:13" ht="30">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="8" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="207.75" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="18">
         <v>8</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="18">
         <v>8</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="33" t="s">
+      <c r="K8" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="33" t="s">
+      <c r="L8" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="M8" s="30"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" spans="1:13" ht="202.5" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="18">
         <v>6</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="18">
         <v>6</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="20" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="203.25" customHeight="1">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="18">
         <v>8</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="18">
         <v>8</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="K10" s="33" t="s">
+      <c r="K10" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="L10" s="33" t="s">
+      <c r="L10" s="20" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="184.5" customHeight="1">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="18">
         <v>8</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="18">
         <v>8</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K11" s="33" t="s">
+      <c r="K11" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="L11" s="33" t="s">
+      <c r="L11" s="20" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="147.75" customHeight="1">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="18">
         <v>6</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="18">
         <v>6</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="L12" s="33" t="s">
+      <c r="L12" s="20" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="11">
         <v>36</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="11">
         <v>36</v>
       </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A13:E13"/>
+  <mergeCells count="12">
+    <mergeCell ref="A16:G22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2353,14 +2455,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
@@ -3042,193 +3144,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="37" t="s">
+      <c r="B2" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="C2" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="D2" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="37" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="23" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="38" t="s">
+      <c r="B3" s="20">
+        <v>36</v>
+      </c>
+      <c r="C3" s="20">
+        <v>36</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="33">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="20">
+        <v>4</v>
+      </c>
+      <c r="C4" s="20">
+        <v>4</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="20">
+        <v>1</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="20">
+        <v>5</v>
+      </c>
+      <c r="C6" s="20">
+        <v>5</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="20">
+        <v>5</v>
+      </c>
+      <c r="C7" s="20">
+        <v>5</v>
+      </c>
+      <c r="D7" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="20">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="20">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="20">
         <v>36</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C10" s="20">
         <v>36</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="33">
-        <v>4</v>
-      </c>
-      <c r="C4" s="33">
-        <v>4</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="33">
+      <c r="D10" s="20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C11" s="24">
         <v>1</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="33">
-        <v>5</v>
-      </c>
-      <c r="C6" s="33">
-        <v>5</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="33">
-        <v>5</v>
-      </c>
-      <c r="C7" s="33">
-        <v>5</v>
-      </c>
-      <c r="D7" s="39">
+      <c r="D11" s="20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="20">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20">
+        <v>32</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="24">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="33">
-        <v>36</v>
-      </c>
-      <c r="C10" s="33">
-        <v>36</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" s="39">
+      <c r="C13" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="39">
-        <v>1</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="33">
-        <v>32</v>
-      </c>
-      <c r="C12" s="33">
-        <v>32</v>
-      </c>
-      <c r="D12" s="33" t="s">
+      <c r="D13" s="20" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="38" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B13" s="39">
-        <v>1</v>
-      </c>
-      <c r="C13" s="39">
-        <v>1</v>
-      </c>
-      <c r="D13" s="33" t="s">
+      <c r="B14" s="20">
+        <v>254</v>
+      </c>
+      <c r="C14" s="20">
+        <v>254</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="33">
-        <v>254</v>
-      </c>
-      <c r="C14" s="33">
-        <v>254</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3236,8 +3338,9 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3252,185 +3355,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="14" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="16" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="14" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="16" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="14" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="16" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="14" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="16" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="14" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="16" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="14" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="16" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="14" t="s">
         <v>217</v>
       </c>
     </row>
